--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486525_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486525_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1017</v>
+        <v>5.4093</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0196</v>
+        <v>4.8957</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.5137</v>
       </c>
       <c r="G2" t="n">
         <v>1.1363</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.0568</v>
+        <v>-0.7493</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4949</v>
+        <v>-0.6189</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5619</v>
+        <v>-0.1304</v>
       </c>
       <c r="V2" t="n">
         <v>2.6297</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3545</v>
+        <v>2.9482</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4079</v>
+        <v>3.4331</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0534</v>
+        <v>-0.4849</v>
       </c>
       <c r="G3" t="n">
         <v>1.1252</v>
@@ -688,13 +688,13 @@
         <v>2.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5343</v>
+        <v>0.128</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3389</v>
+        <v>-0.3136</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8731</v>
+        <v>0.4416</v>
       </c>
       <c r="V3" t="n">
         <v>1.695</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1063</v>
+        <v>2.541</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6958</v>
+        <v>4.0073</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5895</v>
+        <v>-1.4662</v>
       </c>
       <c r="G4" t="n">
         <v>1.952</v>
@@ -766,13 +766,13 @@
         <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5893</v>
+        <v>0.024</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0143</v>
+        <v>0.3257</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4249</v>
+        <v>-0.3016</v>
       </c>
       <c r="V4" t="n">
         <v>0.5649999999999999</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4089</v>
+        <v>0.8446</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5008</v>
+        <v>-0.0327</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9081</v>
+        <v>0.8773</v>
       </c>
       <c r="G5" t="n">
         <v>0.3489</v>
@@ -844,13 +844,13 @@
         <v>0.6525</v>
       </c>
       <c r="S5" t="n">
-        <v>0.233</v>
+        <v>-0.3314</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4627</v>
+        <v>-0.0709</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2297</v>
+        <v>-0.2605</v>
       </c>
       <c r="V5" t="n">
         <v>0.1745</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0291</v>
+        <v>-0.1023</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3755</v>
+        <v>0.4873</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4046</v>
+        <v>-0.5896</v>
       </c>
       <c r="G6" t="n">
         <v>0.8937</v>
@@ -922,13 +922,13 @@
         <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0103</v>
+        <v>-0.0835</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6165</v>
+        <v>-0.5047</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6061</v>
+        <v>0.4212</v>
       </c>
       <c r="V6" t="n">
         <v>-1.13</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. ALDERETE DIAZ</t>
+          <t>M. LAPORNIK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4185</v>
+        <v>-0.1911</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7453</v>
+        <v>-0.003</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3267</v>
+        <v>-0.188</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1464</v>
+        <v>0.6068</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1644</v>
+        <v>-1.9862</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3108</v>
+        <v>2.593</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4517</v>
+        <v>2.9594</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0365</v>
+        <v>-0.5229</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4152</v>
+        <v>3.4823</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3053</v>
+        <v>-2.3526</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2009</v>
+        <v>-1.4633</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1044</v>
+        <v>-0.8893</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6525</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5225</v>
+        <v>2.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1729</v>
+        <v>-0.6234</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2824</v>
+        <v>-0.6128</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1095</v>
+        <v>-0.0105</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7395</v>
+        <v>-0.1745</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.7395</v>
+        <v>-0.1745</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. LAPORNIK</t>
+          <t>D. ALDERETE DIAZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5575</v>
+        <v>-0.2507</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.277</v>
+        <v>-1.6083</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2805</v>
+        <v>1.3575</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6068</v>
+        <v>1.1464</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9862</v>
+        <v>-0.1644</v>
       </c>
       <c r="I8" t="n">
-        <v>2.593</v>
+        <v>1.3108</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9594</v>
+        <v>1.4517</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5229</v>
+        <v>0.0365</v>
       </c>
       <c r="L8" t="n">
-        <v>3.4823</v>
+        <v>1.4152</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.3526</v>
+        <v>-0.3053</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4633</v>
+        <v>-0.2009</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8893</v>
+        <v>-0.1044</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1751</v>
+        <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9898</v>
+        <v>-0.0051</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8868</v>
+        <v>-0.1454</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.103</v>
+        <v>0.1403</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1745</v>
+        <v>-0.7395</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.1745</v>
+        <v>-0.7395</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1538</v>
+        <v>-2.1893</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4731</v>
+        <v>-1.2928</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6807</v>
+        <v>-0.8965</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6074</v>
@@ -1156,13 +1156,13 @@
         <v>0.2175</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7639</v>
+        <v>-0.7994</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.5732</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0105</v>
+        <v>-0.2262</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0758</v>
+        <v>-2.9641</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1975</v>
+        <v>-2.0857</v>
       </c>
       <c r="F10" t="n">
         <v>-0.8784</v>
@@ -1234,10 +1234,10 @@
         <v>0.2175</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.733</v>
+        <v>-0.6213</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4795</v>
+        <v>-0.3677</v>
       </c>
       <c r="U10" t="n">
         <v>-0.2536</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-11.7846</v>
+        <v>-10.7236</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.663</v>
+        <v>-9.787000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1216</v>
+        <v>-0.9366</v>
       </c>
       <c r="G11" t="n">
         <v>-9.0297</v>
@@ -1312,13 +1312,13 @@
         <v>2.3926</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6047</v>
+        <v>-0.5438</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2209</v>
+        <v>-0.3449</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3838</v>
+        <v>-0.1989</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4552</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.047899999999999</v>
+        <v>-4.677999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.356299999999999</v>
+        <v>-1.986100000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6918</v>
+        <v>-2.6917</v>
       </c>
       <c r="G12" t="n">
         <v>-5.032699999999999</v>
@@ -1390,13 +1390,13 @@
         <v>14.1379</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.9748</v>
+        <v>-3.6052</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.5964</v>
+        <v>-3.2264</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3786999999999998</v>
+        <v>-0.3786</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3904000000000005</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8929</v>
+        <v>3.5075</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2587</v>
+        <v>2.8116</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6343</v>
+        <v>0.6959</v>
       </c>
       <c r="G13" t="n">
         <v>0.7294</v>
@@ -1468,13 +1468,13 @@
         <v>0.2175</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9916</v>
+        <v>0.6063</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8051</v>
+        <v>0.3581</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1865</v>
+        <v>0.2481</v>
       </c>
       <c r="V13" t="n">
         <v>4.1294</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. POLANCO TAVAREZ</t>
+          <t>A. JORDA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9008</v>
+        <v>2.5602</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9052</v>
+        <v>1.435</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.0044</v>
+        <v>1.1252</v>
       </c>
       <c r="G14" t="n">
-        <v>3.3643</v>
+        <v>1.7102</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5499000000000001</v>
+        <v>1.1588</v>
       </c>
       <c r="I14" t="n">
-        <v>3.9141</v>
+        <v>0.5514</v>
       </c>
       <c r="J14" t="n">
-        <v>3.46</v>
+        <v>2.6315</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.7475000000000001</v>
+        <v>1.0616</v>
       </c>
       <c r="L14" t="n">
-        <v>4.2074</v>
+        <v>1.5698</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.9213</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1976</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2933</v>
+        <v>-1.0184</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.435</v>
+        <v>-0.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6458</v>
+        <v>0.59</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8172</v>
+        <v>-0.1514</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8287</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.6743</v>
+        <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7156</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.3899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. JORDA RODRIGUEZ</t>
+          <t>E. POLANCO TAVAREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.758</v>
+        <v>2.4422</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6585</v>
+        <v>4.57</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0995</v>
+        <v>-2.1277</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7102</v>
+        <v>3.3643</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1588</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5514</v>
+        <v>3.9141</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6315</v>
+        <v>3.46</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0616</v>
+        <v>-0.7475000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>1.5698</v>
+        <v>4.2074</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9213</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.1976</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0184</v>
+        <v>-0.2933</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.87</v>
+        <v>-0.435</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7877999999999999</v>
+        <v>1.1873</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0721</v>
+        <v>0.4819</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7157</v>
+        <v>0.7054</v>
       </c>
       <c r="V15" t="n">
-        <v>1.13</v>
+        <v>-1.6743</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.7156</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-3.3899</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>S. HOLLANDERS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1434</v>
+        <v>1.4119</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0805</v>
+        <v>-0.0864</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0629</v>
+        <v>1.4984</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6529</v>
+        <v>3.0472</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6051</v>
+        <v>1.1586</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0478</v>
+        <v>1.8885</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7931</v>
+        <v>3.6569</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.8696</v>
+        <v>0.73</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0765</v>
+        <v>2.9269</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1402</v>
+        <v>-0.6097</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2645</v>
+        <v>0.4286</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1243</v>
+        <v>-1.0383</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2175</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8393</v>
+        <v>0.3224</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8736</v>
+        <v>-0.4807</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9657</v>
+        <v>0.803</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. HOLLANDERS</t>
+          <t>U. MENDICOTE RUBIO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3053</v>
+        <v>1.2025</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1982</v>
+        <v>0.4688</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5035</v>
+        <v>0.7338</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0472</v>
+        <v>-0.5002</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1586</v>
+        <v>0.9366</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8885</v>
+        <v>-1.4368</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6569</v>
+        <v>-0.1176</v>
       </c>
       <c r="K17" t="n">
-        <v>0.73</v>
+        <v>0.4745</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9269</v>
+        <v>-0.5921</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6097</v>
+        <v>-0.3826</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4286</v>
+        <v>0.4621</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0383</v>
+        <v>-0.8447</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.9576</v>
+        <v>0.6525</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2157</v>
+        <v>0.6597</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5924</v>
+        <v>0.1959</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8081</v>
+        <v>0.4638</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>U. MENDICOTE RUBIO</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.07340000000000001</v>
+        <v>1.1531</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5371</v>
+        <v>-0.4783</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6105</v>
+        <v>1.6314</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5002</v>
+        <v>-0.6529</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9366</v>
+        <v>-0.6051</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4368</v>
+        <v>-0.0478</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1176</v>
+        <v>-0.7931</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4745</v>
+        <v>-0.8696</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5921</v>
+        <v>0.0765</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3826</v>
+        <v>0.1402</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4621</v>
+        <v>0.2645</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8447</v>
+        <v>-0.1243</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4694</v>
+        <v>0.849</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8099</v>
+        <v>0.3149</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3405</v>
+        <v>0.5341</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3904</v>
+        <v>0.7395</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6137</v>
+        <v>0.2289</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.602</v>
+        <v>-0.1549</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0117</v>
+        <v>0.3839</v>
       </c>
       <c r="G19" t="n">
         <v>1.9462</v>
@@ -1936,13 +1936,13 @@
         <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6251</v>
+        <v>0.2175</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.3509</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1728</v>
+        <v>0.5684</v>
       </c>
       <c r="V19" t="n">
         <v>-1.4997</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5922</v>
+        <v>-0.9911</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.402</v>
+        <v>-1.9549</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8097</v>
+        <v>0.9638</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9227</v>
@@ -2014,13 +2014,13 @@
         <v>0.6525</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1268</v>
+        <v>0.4744</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0769</v>
+        <v>0.3701</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0499</v>
+        <v>0.1042</v>
       </c>
       <c r="V20" t="n">
         <v>-0.1952</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6876</v>
+        <v>-2.159</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2238</v>
+        <v>-2.7826</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5362</v>
+        <v>0.6236</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7732</v>
@@ -2092,13 +2092,13 @@
         <v>1.7401</v>
       </c>
       <c r="S21" t="n">
-        <v>1.413</v>
+        <v>0.9415</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6922</v>
+        <v>0.1334</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7208</v>
+        <v>0.8081</v>
       </c>
       <c r="V21" t="n">
         <v>0.1952</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1323</v>
+        <v>-2.5633</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2481</v>
+        <v>-1.1363</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8842</v>
+        <v>-1.427</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9155</v>
@@ -2170,13 +2170,13 @@
         <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.697</v>
+        <v>-0.128</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6044</v>
+        <v>-0.4927</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0925</v>
+        <v>0.3647</v>
       </c>
       <c r="V22" t="n">
         <v>-2.8249</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>6.047999999999999</v>
+        <v>6.792900000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>2.6917</v>
+        <v>2.692</v>
       </c>
       <c r="F23" t="n">
-        <v>3.3563</v>
+        <v>4.1013</v>
       </c>
       <c r="G23" t="n">
-        <v>5.0328</v>
+        <v>5.032800000000001</v>
       </c>
       <c r="H23" t="n">
         <v>5.232</v>
@@ -2221,10 +2221,10 @@
         <v>-0.1993000000000007</v>
       </c>
       <c r="J23" t="n">
-        <v>8.3049</v>
+        <v>8.304899999999998</v>
       </c>
       <c r="K23" t="n">
-        <v>3.0134</v>
+        <v>3.013399999999999</v>
       </c>
       <c r="L23" t="n">
         <v>5.2913</v>
@@ -2248,16 +2248,16 @@
         <v>9.787699999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>4.9749</v>
+        <v>5.720099999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3787000000000001</v>
+        <v>0.3785999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>4.5964</v>
+        <v>5.3412</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3904000000000001</v>
+        <v>0.3904000000000005</v>
       </c>
       <c r="W23" t="n">
         <v>8.1463</v>
